--- a/prix/diessner.xlsx
+++ b/prix/diessner.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB415B6-41FC-40A3-924B-4147CE8E49A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8BEB4A-E6B3-4F13-8B47-F54D7F5CA2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -310,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -343,13 +343,19 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -732,13 +738,13 @@
       <c r="C2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <v>48.45</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="13">
         <v>-10</v>
       </c>
     </row>
@@ -752,13 +758,13 @@
       <c r="C3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="14">
         <v>110.84</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>9</v>
       </c>
     </row>
@@ -772,13 +778,13 @@
       <c r="C4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="14">
         <v>151.19</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>14</v>
       </c>
     </row>
@@ -792,13 +798,13 @@
       <c r="C5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="14">
         <v>64.489999999999995</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>23</v>
       </c>
     </row>
@@ -812,13 +818,13 @@
       <c r="C6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <v>115.95</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <v>-4</v>
       </c>
     </row>
@@ -832,14 +838,14 @@
       <c r="C7" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="16">
         <v>50.51</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="14">
-        <v>24</v>
+      <c r="F7" s="15">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -852,14 +858,14 @@
       <c r="C8" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="16">
         <v>14.97</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="14">
-        <v>29</v>
+      <c r="F8" s="15">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -872,13 +878,13 @@
       <c r="C9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="15">
-        <v>15.87</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="D9" s="16">
+        <v>14.97</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <v>4</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -893,13 +899,13 @@
       <c r="C10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="16">
         <v>14.97</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="15">
         <v>-1</v>
       </c>
     </row>
@@ -911,13 +917,13 @@
       <c r="C11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="16">
         <v>14.01</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="15">
         <v>9</v>
       </c>
     </row>
@@ -931,13 +937,13 @@
       <c r="C12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="15">
-        <v>32.520000000000003</v>
-      </c>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="16">
+        <v>30.27</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="15">
         <v>8</v>
       </c>
       <c r="G12" s="5" t="s">
@@ -952,14 +958,14 @@
       <c r="C13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="16">
         <v>30.27</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="14">
-        <v>14</v>
+      <c r="F13" s="15">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -970,13 +976,13 @@
       <c r="C14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="16">
         <v>30.27</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="15">
         <v>16</v>
       </c>
     </row>
@@ -990,13 +996,13 @@
       <c r="C15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="15">
-        <v>61.21</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="16">
+        <v>56.71</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="15">
         <v>12</v>
       </c>
       <c r="G15" s="5" t="s">
@@ -1011,14 +1017,14 @@
       <c r="C16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="16">
         <v>56.71</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="14">
-        <v>36</v>
+      <c r="F16" s="15">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1029,13 +1035,13 @@
       <c r="C17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <v>56.71</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="15">
         <v>14</v>
       </c>
     </row>
@@ -1049,14 +1055,14 @@
       <c r="C18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="15">
-        <v>21.05</v>
-      </c>
-      <c r="E18" s="13" t="s">
+      <c r="D18" s="16">
+        <v>20.150000000000002</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="14">
-        <v>7</v>
+      <c r="F18" s="15">
+        <v>6</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>58</v>
@@ -1072,13 +1078,13 @@
       <c r="C19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="15">
-        <v>38.200000000000003</v>
-      </c>
-      <c r="E19" s="13" t="s">
+      <c r="D19" s="16">
+        <v>35.950000000000003</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="15">
         <v>14</v>
       </c>
       <c r="G19" s="5" t="s">
@@ -1095,14 +1101,14 @@
       <c r="C20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="16">
         <v>63.6</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="14">
-        <v>9</v>
+      <c r="F20" s="15">
+        <v>8</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>64</v>
@@ -1118,7 +1124,7 @@
       <c r="C21" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="17">
         <v>224.04</v>
       </c>
       <c r="E21" s="10" t="s">
@@ -1138,8 +1144,8 @@
       <c r="C22" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="12">
-        <v>242.21</v>
+      <c r="D22" s="17">
+        <v>230.96</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>9</v>
@@ -1161,7 +1167,7 @@
       <c r="C23" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="17">
         <v>95.4</v>
       </c>
       <c r="E23" s="10" t="s">
@@ -1181,8 +1187,8 @@
       <c r="C24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="12">
-        <v>96.99</v>
+      <c r="D24" s="17">
+        <v>92.49</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>11</v>

--- a/prix/diessner.xlsx
+++ b/prix/diessner.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE8BEB4A-E6B3-4F13-8B47-F54D7F5CA2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF76D386-C3FA-4532-90A8-ABE251226F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23124" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -310,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -353,9 +353,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -739,13 +736,13 @@
         <v>69</v>
       </c>
       <c r="D2" s="14">
-        <v>48.45</v>
+        <v>50.300000000000004</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="13">
-        <v>-10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -765,7 +762,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="13">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -785,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="13">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -805,7 +802,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="13">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -825,7 +822,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="13">
-        <v>-4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -838,14 +835,14 @@
       <c r="C7" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="14">
         <v>50.51</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="15">
-        <v>23</v>
+      <c r="F7" s="13">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -858,14 +855,14 @@
       <c r="C8" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="14">
         <v>14.97</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="15">
-        <v>28</v>
+      <c r="F8" s="13">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -878,14 +875,14 @@
       <c r="C9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="16">
-        <v>14.97</v>
+      <c r="D9" s="14">
+        <v>15.87</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="15">
-        <v>4</v>
+      <c r="F9" s="13">
+        <v>12</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>58</v>
@@ -899,14 +896,14 @@
       <c r="C10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="14">
         <v>14.97</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="15">
-        <v>-1</v>
+      <c r="F10" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -917,14 +914,14 @@
       <c r="C11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="14">
         <v>14.01</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="15">
-        <v>9</v>
+      <c r="F11" s="13">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -937,14 +934,14 @@
       <c r="C12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="16">
-        <v>30.27</v>
+      <c r="D12" s="14">
+        <v>33.549999999999997</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="15">
-        <v>8</v>
+      <c r="F12" s="13">
+        <v>21</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>57</v>
@@ -958,14 +955,14 @@
       <c r="C13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="16">
-        <v>30.27</v>
+      <c r="D13" s="14">
+        <v>31.3</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="15">
-        <v>13</v>
+      <c r="F13" s="13">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -976,14 +973,14 @@
       <c r="C14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="14">
         <v>30.27</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="15">
-        <v>16</v>
+      <c r="F14" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -996,14 +993,14 @@
       <c r="C15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="16">
-        <v>56.71</v>
+      <c r="D15" s="14">
+        <v>63.03</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="15">
-        <v>12</v>
+      <c r="F15" s="13">
+        <v>15</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>61</v>
@@ -1017,14 +1014,14 @@
       <c r="C16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="14">
         <v>56.71</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="15">
-        <v>32</v>
+      <c r="F16" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1035,13 +1032,13 @@
       <c r="C17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="14">
         <v>56.71</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="13">
         <v>14</v>
       </c>
     </row>
@@ -1055,13 +1052,13 @@
       <c r="C18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="16">
-        <v>20.150000000000002</v>
+      <c r="D18" s="14">
+        <v>21.05</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="13">
         <v>6</v>
       </c>
       <c r="G18" s="5" t="s">
@@ -1078,14 +1075,14 @@
       <c r="C19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="16">
-        <v>35.950000000000003</v>
+      <c r="D19" s="14">
+        <v>38.200000000000003</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="15">
-        <v>14</v>
+      <c r="F19" s="13">
+        <v>13</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>57</v>
@@ -1101,14 +1098,14 @@
       <c r="C20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="16">
-        <v>63.6</v>
+      <c r="D20" s="14">
+        <v>68.099999999999994</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="15">
-        <v>8</v>
+      <c r="F20" s="13">
+        <v>7</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>64</v>
@@ -1124,14 +1121,14 @@
       <c r="C21" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="16">
         <v>224.04</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="11">
-        <v>4</v>
+      <c r="F21" s="15">
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1144,13 +1141,13 @@
       <c r="C22" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="17">
-        <v>230.96</v>
+      <c r="D22" s="16">
+        <v>242.21</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="15">
         <v>5</v>
       </c>
       <c r="G22" s="5" t="s">
@@ -1167,14 +1164,14 @@
       <c r="C23" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <v>95.4</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="11">
-        <v>6</v>
+      <c r="F23" s="15">
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1187,13 +1184,13 @@
       <c r="C24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="17">
-        <v>92.49</v>
+      <c r="D24" s="16">
+        <v>96.99</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="15">
         <v>5</v>
       </c>
       <c r="G24" s="5" t="s">

--- a/prix/diessner.xlsx
+++ b/prix/diessner.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF76D386-C3FA-4532-90A8-ABE251226F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133614B3-D1F3-4FD2-8055-9A8CB82BCB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23124" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -346,6 +346,9 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -353,9 +356,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -692,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:G450"/>
+  <dimension ref="A1:H450"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" style="4" bestFit="1" customWidth="1"/>
@@ -704,7 +704,7 @@
     <col min="7" max="7" width="26.77734375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -725,7 +725,7 @@
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>52</v>
       </c>
@@ -735,17 +735,17 @@
       <c r="C2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="13">
         <v>50.300000000000004</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>52</v>
       </c>
@@ -755,17 +755,17 @@
       <c r="C3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>110.84</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="13">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F3" s="14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>51</v>
       </c>
@@ -775,17 +775,17 @@
       <c r="C4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>151.19</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F4" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>51</v>
       </c>
@@ -795,17 +795,17 @@
       <c r="C5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>64.489999999999995</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F5" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>53</v>
       </c>
@@ -815,17 +815,17 @@
       <c r="C6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>115.95</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="13">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F6" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>53</v>
       </c>
@@ -835,17 +835,17 @@
       <c r="C7" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>50.51</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="13">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>53</v>
       </c>
@@ -855,17 +855,17 @@
       <c r="C8" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>14.97</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>53</v>
       </c>
@@ -875,20 +875,24 @@
       <c r="C9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="14">
-        <v>15.87</v>
+      <c r="D9" s="13">
+        <f>14.97+H9</f>
+        <v>15.870000000000001</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <v>12</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="2" t="s">
         <v>39</v>
@@ -896,17 +900,17 @@
       <c r="C10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>14.97</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="2" t="s">
         <v>40</v>
@@ -914,17 +918,17 @@
       <c r="C11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>14.01</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>53</v>
       </c>
@@ -934,20 +938,24 @@
       <c r="C12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
+        <f>31.3+H12</f>
         <v>33.549999999999997</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>21</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="2" t="s">
         <v>41</v>
@@ -955,17 +963,17 @@
       <c r="C13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>31.3</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="2" t="s">
         <v>42</v>
@@ -973,17 +981,17 @@
       <c r="C14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>30.27</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>53</v>
       </c>
@@ -993,20 +1001,24 @@
       <c r="C15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
+        <f>58.53+H15</f>
         <v>63.03</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="13">
-        <v>15</v>
+      <c r="F15" s="14">
+        <v>14</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -1014,17 +1026,17 @@
       <c r="C16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <v>56.71</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F16" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="2" t="s">
         <v>44</v>
@@ -1032,17 +1044,17 @@
       <c r="C17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <v>56.71</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F17" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>63</v>
       </c>
@@ -1052,20 +1064,24 @@
       <c r="C18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="14">
-        <v>21.05</v>
+      <c r="D18" s="13">
+        <f>20.15+H18</f>
+        <v>21.049999999999997</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="13">
-        <v>6</v>
+      <c r="F18" s="14">
+        <v>5</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>63</v>
       </c>
@@ -1075,20 +1091,23 @@
       <c r="C19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="14">
-        <v>38.200000000000003</v>
+      <c r="D19" s="13">
+        <v>35.950000000000003</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="13">
-        <v>13</v>
+      <c r="F19" s="14">
+        <v>12</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>63</v>
       </c>
@@ -1098,20 +1117,24 @@
       <c r="C20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
+        <f>63.6+H20</f>
         <v>68.099999999999994</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="13">
-        <v>7</v>
+      <c r="F20" s="14">
+        <v>5</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>50</v>
       </c>
@@ -1121,17 +1144,17 @@
       <c r="C21" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="15">
         <v>224.04</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="15">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F21" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>50</v>
       </c>
@@ -1141,20 +1164,24 @@
       <c r="C22" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="15">
+        <f>230.96+H22</f>
         <v>242.21</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="15">
-        <v>5</v>
+      <c r="F22" s="16">
+        <v>2</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>50</v>
       </c>
@@ -1164,17 +1191,17 @@
       <c r="C23" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="15">
         <v>95.4</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="15">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F23" s="16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>50</v>
       </c>
@@ -1184,20 +1211,24 @@
       <c r="C24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
+        <f>92.49+H24</f>
         <v>96.99</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="16">
         <v>5</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1205,7 +1236,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1213,7 +1244,7 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1221,7 +1252,7 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1229,7 +1260,7 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1237,7 +1268,7 @@
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1245,7 +1276,7 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -1253,7 +1284,7 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>

--- a/prix/diessner.xlsx
+++ b/prix/diessner.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133614B3-D1F3-4FD2-8055-9A8CB82BCB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A7D8AD-7388-4FC5-AE0C-EA9BB8A90D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -736,13 +736,13 @@
         <v>69</v>
       </c>
       <c r="D2" s="13">
-        <v>50.300000000000004</v>
+        <v>51.78</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="14">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -762,7 +762,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -782,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -842,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="F7" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -862,7 +862,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="14">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -876,14 +876,13 @@
         <v>68</v>
       </c>
       <c r="D9" s="13">
-        <f>14.97+H9</f>
-        <v>15.870000000000001</v>
+        <v>14.97</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>58</v>
@@ -907,7 +906,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -939,14 +938,13 @@
         <v>67</v>
       </c>
       <c r="D12" s="13">
-        <f>31.3+H12</f>
-        <v>33.549999999999997</v>
+        <v>31.3</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>57</v>
@@ -964,13 +962,13 @@
         <v>49</v>
       </c>
       <c r="D13" s="13">
-        <v>31.3</v>
+        <v>29.05</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1002,8 +1000,7 @@
         <v>66</v>
       </c>
       <c r="D15" s="13">
-        <f>58.53+H15</f>
-        <v>63.03</v>
+        <v>58.53</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>26</v>
@@ -1027,13 +1024,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="13">
-        <v>56.71</v>
+        <v>53.89</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1065,8 +1062,7 @@
         <v>68</v>
       </c>
       <c r="D18" s="13">
-        <f>20.15+H18</f>
-        <v>21.049999999999997</v>
+        <v>20.150000000000002</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>29</v>
@@ -1118,14 +1114,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="13">
-        <f>63.6+H20</f>
-        <v>68.099999999999994</v>
+        <v>61.300000000000004</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>64</v>
@@ -1151,7 +1146,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="16">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1165,8 +1160,7 @@
         <v>65</v>
       </c>
       <c r="D22" s="15">
-        <f>230.96+H22</f>
-        <v>242.21</v>
+        <v>230.96</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>9</v>
@@ -1198,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="F23" s="16">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1212,8 +1206,7 @@
         <v>66</v>
       </c>
       <c r="D24" s="15">
-        <f>92.49+H24</f>
-        <v>96.99</v>
+        <v>92.49</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>11</v>

--- a/prix/diessner.xlsx
+++ b/prix/diessner.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A7D8AD-7388-4FC5-AE0C-EA9BB8A90D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1C691D-60BC-41C6-A45F-A62003C10201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -742,7 +742,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -756,13 +756,13 @@
         <v>70</v>
       </c>
       <c r="D3" s="13">
-        <v>110.84</v>
+        <v>122.91</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="14">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -782,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -842,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="F7" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -876,13 +876,13 @@
         <v>68</v>
       </c>
       <c r="D9" s="13">
-        <v>14.97</v>
+        <v>16.47</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>58</v>
@@ -900,13 +900,13 @@
         <v>48</v>
       </c>
       <c r="D10" s="13">
-        <v>14.97</v>
+        <v>16.47</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="14">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -962,13 +962,13 @@
         <v>49</v>
       </c>
       <c r="D13" s="13">
-        <v>29.05</v>
+        <v>31.080000000000002</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1006,7 +1006,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>61</v>
@@ -1030,7 +1030,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="14">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1094,7 +1094,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>57</v>
@@ -1120,7 +1120,7 @@
         <v>31</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>64</v>
@@ -1146,7 +1146,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1192,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="F23" s="16">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1212,7 +1212,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>61</v>
